--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -479,15 +479,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -501,15 +497,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -523,15 +515,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -545,15 +533,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0.219257</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.18966</v>
       </c>
     </row>
     <row r="8">
@@ -567,15 +551,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -589,15 +569,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -611,15 +587,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>1.799715</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.912572</v>
       </c>
     </row>
     <row r="11">
@@ -633,15 +605,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-1.799715</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-0.912572</v>
       </c>
     </row>
     <row r="12">
@@ -655,15 +623,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -677,15 +641,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -699,15 +659,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -721,15 +677,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -743,15 +695,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.746706</v>
       </c>
     </row>
     <row r="17">
@@ -765,15 +713,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -831,15 +775,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.746706</v>
       </c>
     </row>
     <row r="21">
@@ -853,15 +793,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -875,15 +811,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -933,15 +865,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -955,10 +883,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>69.367318</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -977,15 +903,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.746706</v>
       </c>
     </row>
     <row r="28">
@@ -999,15 +921,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1021,15 +939,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.746706</v>
       </c>
     </row>
     <row r="30">
@@ -1065,15 +979,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1111,20 +1021,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1133,20 +1037,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1155,20 +1053,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1177,20 +1069,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1199,20 +1085,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1221,20 +1101,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1249,10 +1123,8 @@
       <c r="C40" s="3" t="n">
         <v>0.030681</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1261,20 +1133,14 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.0752</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.030681</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1283,20 +1149,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1305,20 +1165,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1327,20 +1181,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1349,20 +1197,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1371,20 +1213,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1393,20 +1229,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1415,20 +1245,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>1.276278</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1.036642</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.158587</v>
       </c>
     </row>
     <row r="49">
@@ -1453,18 +1277,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0.002</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1473,20 +1293,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1495,20 +1309,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1517,20 +1325,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1539,20 +1341,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1583,20 +1379,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1605,20 +1395,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1627,20 +1411,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1649,20 +1427,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1671,20 +1443,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1693,20 +1459,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1715,20 +1475,14 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1769,20 +1523,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1791,20 +1539,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1813,20 +1555,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1835,20 +1571,14 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.092303</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.135746</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.133304</v>
       </c>
     </row>
     <row r="69">
@@ -1857,20 +1587,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1879,20 +1603,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1901,20 +1619,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1923,20 +1635,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1945,20 +1651,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1967,20 +1667,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1989,20 +1683,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2033,20 +1721,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2055,20 +1737,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2077,20 +1753,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2121,20 +1791,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2143,20 +1807,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2165,20 +1823,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2187,20 +1839,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2209,20 +1855,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2269,20 +1909,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>4.514431</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>5.585721</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>5.585721</v>
       </c>
     </row>
     <row r="89">
@@ -2291,20 +1925,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2329,20 +1957,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2367,20 +1989,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2389,20 +2005,14 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>1.04496</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.771989</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.025283</v>
       </c>
     </row>
     <row r="95">
@@ -2411,20 +2021,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2477,15 +2081,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.746706</v>
       </c>
     </row>
     <row r="100">
@@ -2499,15 +2099,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2521,15 +2117,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0.044519</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.030681</v>
       </c>
     </row>
     <row r="102">
@@ -2543,15 +2135,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2565,15 +2153,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="104">
@@ -2587,15 +2171,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.09426900000000001</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.009286000000000001</v>
       </c>
     </row>
     <row r="105">
@@ -2609,15 +2189,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2631,15 +2207,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.213788</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.069967</v>
       </c>
     </row>
     <row r="107">
@@ -2653,15 +2225,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0.184688</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2675,15 +2243,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2697,15 +2261,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2719,15 +2279,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2741,15 +2297,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2763,15 +2315,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2785,15 +2333,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2807,15 +2351,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2829,15 +2369,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2851,15 +2387,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2873,15 +2405,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2895,15 +2423,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2917,10 +2441,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>0.0095</v>
@@ -2937,15 +2459,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2959,15 +2477,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2981,15 +2495,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3003,15 +2513,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3025,15 +2531,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3047,15 +2549,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3069,15 +2567,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3113,15 +2607,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>-0.07801</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>-0.003703</v>
       </c>
     </row>
     <row r="129">
@@ -3171,15 +2661,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3211,15 +2697,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.87035</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.035209</v>
       </c>
     </row>
     <row r="134">
@@ -3233,15 +2715,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3255,15 +2733,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-1.211477</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.840938</v>
       </c>
     </row>
   </sheetData>
@@ -3533,7 +3007,11 @@
           <t>Non-currentAssets total</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3623,7 +3101,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>Flow through share premium liability (Note</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3841,7 +3319,11 @@
           <t>Loss for the year</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3992,7 +3474,11 @@
           <t>Share-based payments</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -4052,7 +3538,11 @@
           <t>Prepaid expense</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4110,7 +3600,11 @@
           <t>Other receivables</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4139,7 +3633,11 @@
           <t>Trade and other payables</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4360,7 +3858,11 @@
           <t>Share issuance costs</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4488,7 +3990,11 @@
           <t>Cash, end of the year</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4641,7 +4147,11 @@
           <t>Share issuance costs included in accounts payable</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4672,7 +4182,11 @@
           <t>Management fees (Note 9)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4734,7 +4248,11 @@
           <t>Consulting fees</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4763,7 +4281,11 @@
           <t>Filing fees</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4852,7 +4374,11 @@
           <t>Office and general</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4881,7 +4407,11 @@
           <t>Expenses total</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -429,13 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -466,6 +467,11 @@
           <t>2024-12</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -491,6 +497,9 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -509,6 +518,9 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -527,6 +539,9 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -545,6 +560,9 @@
       <c r="D7" s="3" t="n">
         <v>0.18966</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>0.14457</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -563,6 +581,9 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -581,6 +602,9 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -599,6 +623,9 @@
       <c r="D10" s="3" t="n">
         <v>0.912572</v>
       </c>
+      <c r="E10" s="3" t="n">
+        <v>0.526253</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -617,6 +644,9 @@
       <c r="D11" s="3" t="n">
         <v>-0.912572</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.526253</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -635,6 +665,9 @@
       <c r="D12" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -648,10 +681,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -671,6 +707,9 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -689,6 +728,9 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -707,6 +749,9 @@
       <c r="D16" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -720,10 +765,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -747,6 +795,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -769,6 +822,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -787,6 +845,9 @@
       <c r="D20" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -805,6 +866,9 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -823,6 +887,9 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -841,6 +908,9 @@
       <c r="D23" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -859,6 +929,9 @@
       <c r="D24" s="3" t="n">
         <v>-0.01</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -877,6 +950,9 @@
       <c r="D25" s="3" t="n">
         <v>-0.01</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -897,6 +973,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -915,6 +996,9 @@
       <c r="D27" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -933,6 +1017,9 @@
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -951,6 +1038,9 @@
       <c r="D29" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -973,6 +1063,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -991,6 +1086,9 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1013,6 +1111,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1036,6 +1139,9 @@
       <c r="D34" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1052,6 +1158,9 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1068,6 +1177,9 @@
       <c r="D36" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1084,6 +1196,9 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1100,6 +1215,9 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1116,6 +1234,9 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1132,6 +1253,9 @@
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1148,6 +1272,9 @@
       <c r="D41" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1164,6 +1291,9 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1180,6 +1310,9 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1196,6 +1329,9 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1212,6 +1348,9 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1228,6 +1367,9 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1244,6 +1386,9 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1260,6 +1405,9 @@
       <c r="D48" s="3" t="n">
         <v>0.158587</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>0.567451</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1276,6 +1424,9 @@
       <c r="D49" s="3" t="n">
         <v>0.158587</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>0.567451</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1292,6 +1443,9 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1308,6 +1462,9 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1324,6 +1481,9 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1340,6 +1500,9 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1356,6 +1519,9 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1378,6 +1544,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1394,6 +1565,9 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1410,6 +1584,9 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1426,6 +1603,9 @@
       <c r="D58" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1442,6 +1622,9 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1458,6 +1641,9 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1474,6 +1660,9 @@
       <c r="D61" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1490,6 +1679,9 @@
       <c r="D62" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1506,6 +1698,9 @@
       <c r="D63" s="3" t="n">
         <v>0.158587</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>0.567451</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1522,6 +1717,9 @@
       <c r="D64" s="3" t="n">
         <v>0.133304</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>0.148569</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1538,6 +1736,9 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1554,6 +1755,9 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1570,6 +1774,9 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1586,6 +1793,9 @@
       <c r="D68" s="3" t="n">
         <v>0.133304</v>
       </c>
+      <c r="E68" s="3" t="n">
+        <v>0.148569</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1602,6 +1812,9 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1618,6 +1831,9 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1634,6 +1850,9 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1650,6 +1869,9 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1666,6 +1888,9 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1682,6 +1907,9 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1698,6 +1926,9 @@
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1720,6 +1951,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1736,6 +1972,9 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1752,6 +1991,9 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1768,6 +2010,9 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1790,6 +2035,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1806,6 +2056,9 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1822,6 +2075,9 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1838,6 +2094,9 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1854,6 +2113,9 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1870,6 +2132,9 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1892,6 +2157,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1908,6 +2178,9 @@
       <c r="D87" s="3" t="n">
         <v>0.133304</v>
       </c>
+      <c r="E87" s="3" t="n">
+        <v>0.16418</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1924,6 +2197,9 @@
       <c r="D88" s="3" t="n">
         <v>5.585721</v>
       </c>
+      <c r="E88" s="3" t="n">
+        <v>6.341237</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1940,6 +2216,9 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1956,6 +2235,9 @@
       <c r="D90" s="3" t="n">
         <v>-6.373</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>-6.898805</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1972,6 +2254,9 @@
       <c r="D91" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1988,6 +2273,9 @@
       <c r="D92" s="3" t="n">
         <v>0.812562</v>
       </c>
+      <c r="E92" s="3" t="n">
+        <v>0.960839</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -2004,6 +2292,9 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -2020,6 +2311,9 @@
       <c r="D94" s="3" t="n">
         <v>0.025283</v>
       </c>
+      <c r="E94" s="3" t="n">
+        <v>0.403271</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2036,6 +2330,9 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2052,6 +2349,9 @@
       <c r="D96" s="3" t="n">
         <v>0.025283</v>
       </c>
+      <c r="E96" s="3" t="n">
+        <v>0.403271</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -2068,6 +2368,9 @@
       <c r="D97" s="3" t="n">
         <v>0.1594266869289412</v>
       </c>
+      <c r="E97" s="3" t="n">
+        <v>0.7106710535359</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2093,6 +2396,9 @@
       <c r="D99" s="3" t="n">
         <v>-0.746706</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.525805</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -2111,6 +2417,9 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2129,6 +2438,9 @@
       <c r="D101" s="3" t="n">
         <v>0.030681</v>
       </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -2147,6 +2459,9 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -2165,6 +2480,9 @@
       <c r="D103" s="3" t="n">
         <v>0.03</v>
       </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2183,6 +2501,9 @@
       <c r="D104" s="3" t="n">
         <v>0.009286000000000001</v>
       </c>
+      <c r="E104" s="3" t="n">
+        <v>0.125959</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2201,6 +2522,9 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -2219,6 +2543,9 @@
       <c r="D106" s="3" t="n">
         <v>0.069967</v>
       </c>
+      <c r="E106" s="3" t="n">
+        <v>0.125959</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -2237,6 +2564,9 @@
       <c r="D107" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E107" s="3" t="n">
+        <v>0.01545</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2255,6 +2585,9 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -2273,6 +2606,9 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -2291,6 +2627,9 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -2309,6 +2648,9 @@
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -2327,6 +2669,9 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -2345,6 +2690,9 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -2363,6 +2711,9 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -2381,6 +2732,9 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2399,6 +2753,9 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -2417,6 +2774,9 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -2435,6 +2795,9 @@
       <c r="D118" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2453,6 +2816,9 @@
       <c r="D119" s="3" t="n">
         <v>0.0095</v>
       </c>
+      <c r="E119" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2471,6 +2837,9 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2489,6 +2858,9 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2507,6 +2879,9 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2525,6 +2900,9 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2543,6 +2921,9 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2561,6 +2942,9 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2579,6 +2963,9 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2601,6 +2988,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2619,6 +3011,9 @@
       <c r="D128" s="3" t="n">
         <v>-0.003703</v>
       </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2637,6 +3032,9 @@
       <c r="D129" s="3" t="n">
         <v>-0.003703</v>
       </c>
+      <c r="E129" s="3" t="n">
+        <v>0.49066</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2655,6 +3053,9 @@
       <c r="D130" s="3" t="n">
         <v>0.87035</v>
       </c>
+      <c r="E130" s="3" t="n">
+        <v>0.035209</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -2673,6 +3074,9 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2691,6 +3095,9 @@
       <c r="D132" s="3" t="n">
         <v>-0.835141</v>
       </c>
+      <c r="E132" s="3" t="n">
+        <v>0.288908</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -2709,6 +3116,9 @@
       <c r="D133" s="3" t="n">
         <v>0.035209</v>
       </c>
+      <c r="E133" s="3" t="n">
+        <v>0.324117</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2727,6 +3137,9 @@
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -2744,6 +3157,9 @@
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.840938</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.201752</v>
       </c>
     </row>
   </sheetData>
@@ -2757,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2802,6 +3218,11 @@
           <t>2024</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2833,6 +3254,9 @@
       <c r="G2" s="5" t="n">
         <v>0.035209</v>
       </c>
+      <c r="H2" s="5" t="n">
+        <v>0.324117</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2864,6 +3288,9 @@
       <c r="G3" s="5" t="n">
         <v>0.123378</v>
       </c>
+      <c r="H3" s="5" t="n">
+        <v>0.030734</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2878,24 +3305,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Other receivables</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OtherReceivables</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0.0752</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.030681</v>
+          <t>Subscriptions receivable</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.2126</v>
       </c>
     </row>
     <row r="5">
@@ -2911,24 +3341,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prepaid expense</t>
+          <t>Total Current Assets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.105</v>
+        <v>1.351478</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.067323</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.158587</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.567451</v>
       </c>
     </row>
     <row r="6">
@@ -2944,23 +3375,30 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Total Current Assets</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1.351478</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>1.067323</v>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.158587</v>
       </c>
+      <c r="H6" s="5" t="n">
+        <v>0.567451</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2970,17 +3408,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Non-currentAssets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Investment (Note 8)</t>
+          <t>Trade and other payables (Note 8)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>InvestmentsAndAdvances</t>
+          <t>AccountsPayable</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2988,13 +3426,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.133304</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.148569</v>
       </c>
     </row>
     <row r="8">
@@ -3005,31 +3446,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Non-currentAssets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Non-currentAssets total</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
+          <t>Flow-through share premium liability (Note 11)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
-        <v>0.002</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.015611</v>
       </c>
     </row>
     <row r="9">
@@ -3040,27 +3482,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non-currentAssets</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Total Assets</t>
+          <t>Total Liabilities</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TotalAssets</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1.351478</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1.069323</v>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.158587</v>
+        <v>0.133304</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.16418</v>
       </c>
     </row>
     <row r="10">
@@ -3071,27 +3520,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Current Liabilities</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tradeand other payables (Note 9)</t>
+          <t>Share capital (Note 5)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AccountsPayable</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0.092303</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.135746</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.133304</v>
+        <v>5.585721</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.341237</v>
       </c>
     </row>
     <row r="11">
@@ -3102,25 +3558,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Flow through share premium liability (Note</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Flow through share premium liability (Note</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>0.214215</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.161588</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Contributed surplus (Note 5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.812562</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.960839</v>
       </c>
     </row>
     <row r="12">
@@ -3131,27 +3596,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flow through share premium liability (Note</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0.306518</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>0.297334</v>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.133304</v>
+        <v>-6.373</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-6.898805</v>
       </c>
     </row>
     <row r="13">
@@ -3162,27 +3634,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shareholders Equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Share capital (Note 7)</t>
+          <t>Total Equity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>4.514431</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>5.585721</v>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>5.585721</v>
+        <v>0.025283</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.403271</v>
       </c>
     </row>
     <row r="14">
@@ -3193,27 +3672,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Shareholders Equity</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contributed surplus (Note 7)</t>
+          <t>Total Liabilities and Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>0.630742</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0.812562</v>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.812562</v>
+        <v>0.158587</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.567451</v>
       </c>
     </row>
     <row r="15">
@@ -3224,27 +3710,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Shareholders Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>OtherReceivables</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>-4.100213</v>
+        <v>0.0752</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-5.626294</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>-6.373</v>
+        <v>0.030681</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -3255,27 +3748,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shareholders Equity</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Total Equity</t>
+          <t>Prepaid expense</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TotalEquityGrossMinorityInterest</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1.04496</v>
+        <v>0.105</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.771989</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.025283</v>
+        <v>0.03</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -3286,48 +3786,57 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shareholders Equity</t>
+          <t>Non-current Assets</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders Equity</t>
+          <t>Investment (Note 8)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>1.351478</v>
+          <t>InvestmentsAndAdvances</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F17" s="5" t="n">
-        <v>1.069323</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.158587</v>
+        <v>0.002</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Non-current Assets</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Non-current Assets total</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalNonCurrentAssets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3336,98 +3845,120 @@
         </is>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-1.526081</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>-0.746706</v>
+        <v>0.002</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Non-current Assets</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TotalAssets</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.351478</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-0.001866</v>
+        <v>1.069323</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.008024999999999999</v>
+        <v>0.158587</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gain on investment disposal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Trade and other payables (Note 9)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AccountsPayable</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.092303</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.135746</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0075</v>
+        <v>0.133304</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Flow through share premium liability (Note</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shares issued for exploration expenditures</t>
+          <t>Flow through share premium liability (Note</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="5" t="n">
+        <v>0.214215</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.24615</v>
+        <v>0.161588</v>
       </c>
       <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3436,29 +3967,34 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Flow through share premium liability (Note</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shares received on recovery of exploration expenditures</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.306518</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="G22" t="inlineStr">
+        <v>0.297334</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.133304</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3467,33 +4003,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Share capital (Note 7)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>4.514431</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.184688</v>
-      </c>
-      <c r="G23" t="inlineStr">
+        <v>5.585721</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>5.585721</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3502,125 +4039,145 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Recovery of flow through premium</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Contributed surplus (Note 7)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.630742</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.225752</v>
+        <v>0.812562</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.161588</v>
+        <v>0.812562</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prepaid expense</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>-4.100213</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.075</v>
+        <v>-5.626294</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.03</v>
+        <v>-6.373</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sales taxes receivable</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1.04496</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.096701</v>
+        <v>0.771989</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.012914</v>
+        <v>0.025283</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other receivables</t>
+          <t>Total Liabilities and Shareholders¶ Equity</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>1.351478</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.044519</v>
+        <v>1.069323</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.030681</v>
+        <v>0.158587</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3631,17 +4188,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trade and other payables</t>
+          <t>Loss for the year</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3650,10 +4207,13 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.09056599999999999</v>
+        <v>-1.526081</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.009286000000000001</v>
+        <v>-0.746706</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.525805</v>
       </c>
     </row>
     <row r="29">
@@ -3664,29 +4224,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in operating assets and liabilities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-1.211477</v>
+        <v>-0.001866</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.840938</v>
+        <v>-0.008024999999999999</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -3697,12 +4258,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Investment disposal</t>
+          <t>Gain on investment disposal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -3717,7 +4278,12 @@
         </is>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0095</v>
+        <v>-0.0075</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3728,19 +4294,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash flows from investing activities</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Shares issued for exploration and evaluation expenditures</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3751,8 +4313,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="5" t="n">
-        <v>0.0095</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="32">
@@ -3763,27 +4330,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sharesissued inflow-through</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.637</v>
+        <v>0.184688</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.01545</v>
       </c>
     </row>
     <row r="33">
@@ -3794,12 +4368,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Warrants exercised</t>
+          <t>Recovery of flow through premium</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3809,9 +4383,12 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.38165</v>
-      </c>
-      <c r="G33" t="inlineStr">
+        <v>-0.225752</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>-0.161588</v>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3825,24 +4402,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Options exercised</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Prepaid expense</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="G34" t="inlineStr">
+        <v>0.075</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3856,29 +4440,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Sales taxes receivable</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.07801</v>
+        <v>-0.096701</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.003703</v>
+        <v>0.012914</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.092644</v>
       </c>
     </row>
     <row r="36">
@@ -3889,17 +4472,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3908,10 +4491,15 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.95014</v>
+        <v>0.044519</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.003703</v>
+        <v>0.030681</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3922,17 +4510,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Trade and other payables</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3941,10 +4529,13 @@
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-0.261337</v>
+        <v>0.09056599999999999</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.835141</v>
+        <v>0.009286000000000001</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.125959</v>
       </c>
     </row>
     <row r="38">
@@ -3955,17 +4546,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Cash flows used inoperating activities</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3973,11 +4564,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>1.131687</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.87035</v>
+        <v>-0.840938</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>-0.201752</v>
       </c>
     </row>
     <row r="39">
@@ -3988,29 +4584,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash, end of the year</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Investment disposal</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F39" s="5" t="n">
-        <v>0.87035</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.035209</v>
+        <v>0.0095</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -4021,24 +4620,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supplemental disclosure on cash flow information</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Flow through premium</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Cash flows from investing activities</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>0.173125</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4052,12 +4660,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supplemental disclosure on cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Transfer fair value of options exercised</t>
+          <t>Units issued under private placement</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4066,13 +4674,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.00959</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.18366</v>
       </c>
     </row>
     <row r="42">
@@ -4083,12 +4696,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supplemental disclosure on cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Transfer fair value of warrants exercised</t>
+          <t>Units issued under flow-through private placements</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4097,13 +4710,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.00813</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.327</v>
       </c>
     </row>
     <row r="43">
@@ -4114,27 +4732,32 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supplemental disclosure on cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fair value of broker warrants issued</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.014852</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07801</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>-0.003703</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="44">
@@ -4145,17 +4768,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supplemental disclosure on cash flow information</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Share issuance costs included in accounts payable</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4164,33 +4787,34 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.003703</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.95014</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-0.003703</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.49066</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
+          <t>Net change in cash</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4199,31 +4823,34 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.066</v>
+        <v>-0.261337</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.06875000000000001</v>
+        <v>-0.835141</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.288908</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4232,31 +4859,34 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.109722</v>
+        <v>1.131687</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.105991</v>
+        <v>0.87035</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.035209</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Cash, end of the year</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4265,59 +4895,65 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.035</v>
+        <v>0.87035</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.01164</v>
+        <v>0.035209</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.324117</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental disclosure on non-cash information</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Trade settlement in consideration of shares</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>0.004335</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.004048</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.110694</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental disclosure on non-cash information</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Explorationand evaluationexpenditures (Note 8)</t>
+          <t>Flow-through share premium</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -4326,27 +4962,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F49" s="5" t="n">
-        <v>1.288048</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.6169210000000001</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.015611</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Subscriptions receivable under non and flow-through private</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 6,9)</t>
+          <t>Subscriptions receivable under non and flow-through private placements</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -4355,95 +4998,106 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.184688</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.2126</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Subscriptions receivable under non and flow-through private</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Attributed value to warrants issued under private placements</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.113922</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.105222</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.037865</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Attributed value to warrants issued under flow-through private</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Attributed value to warrants issued under flow-through private placements</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>1.799715</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.912572</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.08606800000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Attributed value to warrants issued under flow-through private</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Recovery of flow through premium(Note 12)</t>
+          <t>Attributes value to warrants issued as share issue expenses</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -4452,60 +5106,68 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>-0.225752</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.161588</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>0.008894000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Additional information</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Interest (income)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>-0.046016</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.011247</v>
+        <v>0.003117</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0.000448</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gain on investment disposal</t>
+          <t>Shares issued for exploration expenditures</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4514,29 +5176,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0075</v>
+      <c r="F55" s="5" t="n">
+        <v>0.24615</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
+          <t>Shares received on recovery of exploration expenditures</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4546,31 +5213,38 @@
         </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.001866</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.008024999999999999</v>
+        <v>-0.002</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Changes in operating assets and liabilities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Cash flows used in operating activities</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4579,59 +5253,67 @@
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-1.526081</v>
+        <v>-1.211477</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.746706</v>
+        <v>-0.840938</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Shares issued in flow-through</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-2.2e-08</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.637</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic and</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic and diluted)</t>
+          <t>Warrants exercised</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -4641,10 +5323,1629 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Options exercised</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure on cash flow information</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Flow through premium</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.173125</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure on cash flow information</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Transfer fair value of options exercised</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure on cash flow information</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Transfer fair value of warrants exercised</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0.00813</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure on cash flow information</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Fair value of broker warrants issued</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.014852</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supplemental disclosure on cash flow information</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Share issuance costs included in accounts payable</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.003703</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Management fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.06875000000000001</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.0693</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.109722</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.105991</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.084867</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.01164</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.016592</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Filing fees</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.004335</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.004048</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.004218</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (Note 7)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.6169210000000001</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0.281366</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 5 and 8)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.01545</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0.113922</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.105222</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0.05446</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1.799715</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.912572</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0.526253</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Recovery of flow-through premium (Note 11)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>-0.161588</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Interest (income)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-0.046016</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.011247</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>-0.000448</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Gain on investment disposal</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Gain on debt settlement</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-0.001866</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-0.008024999999999999</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-1.526081</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-0.746706</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-0.525805</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>-2.2e-08</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="n">
         <v>69.14402200000001</v>
       </c>
-      <c r="G59" s="5" t="n">
+      <c r="G80" s="5" t="n">
         <v>78.490571</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>83.609582</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SHARES     CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2024 78,490,571 5,585,721 812,562</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.771989</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>-5.626294</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SHARES     CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.746706</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>-0.746706</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SHARES     CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 78,490,571 5,585,721 812,562</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.025283</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>-6.373</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Balance, January 1, 2025 78,490,571 5,585,721 812,562</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.025283</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>-6.373</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Units issued under private placements 7,673,200 345,795 37,865</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Units issued under flow-through private placements 4,851,429 253,532 86,068</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Attributed value of flow-through share premium liability - (15,611)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-0.015611</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Shares issued expenses - (28,894) 8,894</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Shares issued for mining property acquisition 3,000,000 90,000 -</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Shares issued for debt settlement 3,162,682 110,694 -</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.110694</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Share based payments - - 15,450</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Shares to be issued under private placements (100,200) - -</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Shares to be issued under flow-throuh private placements (70,000) - -</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.525805</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.525805</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SHARES      CAPITAL        SURPLUS       DEFICIT     EQUITY</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2025 97,007,682 6,341,237 960,839</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.403271</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-6.898805</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.06875000000000001</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (Note 8)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.288048</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.6169210000000001</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 6,9)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.184688</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Recovery of flow through premium(Note 12)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-0.225752</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.161588</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TO EQ 1,044,960 637,000 (173,125) 381,650 9,500 184,688 246,150 (32,753) (1,526,081) 771,989</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.025283</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-0.746706</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and total</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.812562</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (basic and</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DEFIC (4,100,213) (1,526,081) (5,626,294)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-6.373</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.746706</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>5.585721</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CO total</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>78.490571</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="119">
@@ -4302,7 +4302,11 @@
           <t>Shares issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -660,13 +660,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046016</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.011247</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000448</v>
       </c>
     </row>
     <row r="13">
@@ -991,13 +991,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.526081</v>
+        <v>-1.480065</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.746706</v>
+        <v>-0.757953</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.525805</v>
+        <v>-0.525357</v>
       </c>
     </row>
     <row r="28">
@@ -1033,13 +1033,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.526081</v>
+        <v>-1.480065</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.746706</v>
+        <v>-0.757953</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.525805</v>
+        <v>-0.525357</v>
       </c>
     </row>
     <row r="30">
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.131687</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.87035</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.035209</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.324117</v>
       </c>
     </row>
     <row r="35">
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.131687</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.87035</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.035209</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.324117</v>
       </c>
     </row>
     <row r="37">
@@ -1397,16 +1397,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.276278</v>
+        <v>0.144591</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.036642</v>
+        <v>0.166292</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.158587</v>
+        <v>0.123378</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.567451</v>
+        <v>0.243334</v>
       </c>
     </row>
     <row r="49">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOC.xlsx
+++ b/output/pdf_financials_xlsx/MOC.xlsx
@@ -4672,7 +4672,11 @@
           <t>Units issued under private placement</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
